--- a/docentes/Caballero Rosas María Teresa - Estadisticos 20212.xlsx
+++ b/docentes/Caballero Rosas María Teresa - Estadisticos 20212.xlsx
@@ -474,16 +474,19 @@
         <v>44</v>
       </c>
       <c r="D2">
-        <v>44</v>
+        <v>12</v>
       </c>
       <c r="E2">
         <v>0</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>72.73</v>
+      </c>
+      <c r="H2">
+        <v>7.7</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -497,16 +500,19 @@
         <v>44</v>
       </c>
       <c r="D3">
-        <v>44</v>
+        <v>14</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>63.64</v>
+      </c>
+      <c r="H3">
+        <v>6.6</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -520,16 +526,19 @@
         <v>35</v>
       </c>
       <c r="D4">
-        <v>35</v>
+        <v>1</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>88.56999999999999</v>
+      </c>
+      <c r="H4">
+        <v>8.6</v>
       </c>
     </row>
   </sheetData>
@@ -585,7 +594,7 @@
         <v>44</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="F2">
         <v>0</v>
@@ -608,7 +617,7 @@
         <v>44</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F3">
         <v>0</v>
@@ -631,7 +640,7 @@
         <v>35</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="F4">
         <v>0</v>
@@ -690,16 +699,19 @@
         <v>44</v>
       </c>
       <c r="D2">
-        <v>44</v>
+        <v>12</v>
       </c>
       <c r="E2">
         <v>0</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>72.73</v>
+      </c>
+      <c r="H2">
+        <v>7.7</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -713,16 +725,19 @@
         <v>44</v>
       </c>
       <c r="D3">
-        <v>44</v>
+        <v>14</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>63.64</v>
+      </c>
+      <c r="H3">
+        <v>6.7</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -736,16 +751,19 @@
         <v>35</v>
       </c>
       <c r="D4">
-        <v>35</v>
+        <v>1</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>88.56999999999999</v>
+      </c>
+      <c r="H4">
+        <v>8.6</v>
       </c>
     </row>
   </sheetData>

--- a/docentes/Caballero Rosas María Teresa - Estadisticos 20212.xlsx
+++ b/docentes/Caballero Rosas María Teresa - Estadisticos 20212.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="174" uniqueCount="82">
   <si>
     <t>Mat</t>
   </si>
@@ -74,6 +74,195 @@
   </si>
   <si>
     <t>Reprobadas</t>
+  </si>
+  <si>
+    <t>ALDUCIN</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>MIXCOHUA</t>
+  </si>
+  <si>
+    <t>FRANCO</t>
+  </si>
+  <si>
+    <t>LOPEZ</t>
+  </si>
+  <si>
+    <t>COUDER</t>
+  </si>
+  <si>
+    <t>ACEVEDO</t>
+  </si>
+  <si>
+    <t>DOMINGUEZ</t>
+  </si>
+  <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>MADRAZO</t>
+  </si>
+  <si>
+    <t>MORALES</t>
+  </si>
+  <si>
+    <t>NAVARRO</t>
+  </si>
+  <si>
+    <t>REYES</t>
+  </si>
+  <si>
+    <t>ARIAS</t>
+  </si>
+  <si>
+    <t>CASTILLO</t>
+  </si>
+  <si>
+    <t>CHICO</t>
+  </si>
+  <si>
+    <t>HUERTA</t>
+  </si>
+  <si>
+    <t>JUSTO</t>
+  </si>
+  <si>
+    <t>MOTA</t>
+  </si>
+  <si>
+    <t>OFICIAL</t>
+  </si>
+  <si>
+    <t>OLMOS</t>
+  </si>
+  <si>
+    <t>RAMOS</t>
+  </si>
+  <si>
+    <t>ROMERO</t>
+  </si>
+  <si>
+    <t>CAMPOS</t>
+  </si>
+  <si>
+    <t>IXMATLAHUA</t>
+  </si>
+  <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
+    <t>TETLA</t>
+  </si>
+  <si>
+    <t>VALENCIA</t>
+  </si>
+  <si>
+    <t>GARCIA</t>
+  </si>
+  <si>
+    <t>0</t>
+  </si>
+  <si>
+    <t>DE LA CRUZ</t>
+  </si>
+  <si>
+    <t>BENITO</t>
+  </si>
+  <si>
+    <t>GIL</t>
+  </si>
+  <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>NEGRETE</t>
+  </si>
+  <si>
+    <t>CERON</t>
+  </si>
+  <si>
+    <t>VILLASEÑOR</t>
+  </si>
+  <si>
+    <t>SOLANO</t>
+  </si>
+  <si>
+    <t>MELANI PAOLA</t>
+  </si>
+  <si>
+    <t>MARIA TERESA</t>
+  </si>
+  <si>
+    <t>ANGELINA</t>
+  </si>
+  <si>
+    <t>CRISTOPHER</t>
+  </si>
+  <si>
+    <t>JOSE RAFAEL</t>
+  </si>
+  <si>
+    <t>YULIANA</t>
+  </si>
+  <si>
+    <t>JESE YAEL</t>
+  </si>
+  <si>
+    <t>YARELI</t>
+  </si>
+  <si>
+    <t>JESUS EMMANUEL</t>
+  </si>
+  <si>
+    <t>RICARDO ABEL</t>
+  </si>
+  <si>
+    <t>ANGELO RENE</t>
+  </si>
+  <si>
+    <t>DULCE MARIA</t>
+  </si>
+  <si>
+    <t>DULCE NAOMI</t>
+  </si>
+  <si>
+    <t>DUILIO</t>
+  </si>
+  <si>
+    <t>JAZMIN</t>
+  </si>
+  <si>
+    <t>VANESSA</t>
+  </si>
+  <si>
+    <t>ATZIRI</t>
+  </si>
+  <si>
+    <t>YULIET</t>
+  </si>
+  <si>
+    <t>MARIA MICHELLE</t>
+  </si>
+  <si>
+    <t>ANGEL DIEGO</t>
+  </si>
+  <si>
+    <t>MONICA AIME</t>
+  </si>
+  <si>
+    <t>ARACELY</t>
+  </si>
+  <si>
+    <t>SAYURI BETSABE</t>
+  </si>
+  <si>
+    <t>ANA LAURA</t>
+  </si>
+  <si>
+    <t>DIEGO EMILIO</t>
   </si>
 </sst>
 </file>
@@ -773,7 +962,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G1"/>
+  <dimension ref="A1:G26"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -803,6 +992,581 @@
         <v>18</v>
       </c>
     </row>
+    <row r="2" spans="1:7">
+      <c r="A2">
+        <v>21330051920252</v>
+      </c>
+      <c r="B2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D2" t="s">
+        <v>57</v>
+      </c>
+      <c r="E2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3">
+        <v>21330051920260</v>
+      </c>
+      <c r="B3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C3" t="s">
+        <v>42</v>
+      </c>
+      <c r="D3" t="s">
+        <v>58</v>
+      </c>
+      <c r="E3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4">
+        <v>21330051920088</v>
+      </c>
+      <c r="B4" t="s">
+        <v>21</v>
+      </c>
+      <c r="C4" t="s">
+        <v>43</v>
+      </c>
+      <c r="D4" t="s">
+        <v>59</v>
+      </c>
+      <c r="E4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5">
+        <v>21330051920337</v>
+      </c>
+      <c r="B5" t="s">
+        <v>22</v>
+      </c>
+      <c r="C5" t="s">
+        <v>33</v>
+      </c>
+      <c r="D5" t="s">
+        <v>60</v>
+      </c>
+      <c r="E5" t="s">
+        <v>8</v>
+      </c>
+      <c r="F5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6">
+        <v>20330051920235</v>
+      </c>
+      <c r="B6" t="s">
+        <v>23</v>
+      </c>
+      <c r="C6" t="s">
+        <v>44</v>
+      </c>
+      <c r="D6" t="s">
+        <v>61</v>
+      </c>
+      <c r="E6" t="s">
+        <v>8</v>
+      </c>
+      <c r="F6" t="s">
+        <v>11</v>
+      </c>
+      <c r="G6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7">
+        <v>19330051920276</v>
+      </c>
+      <c r="B7" t="s">
+        <v>24</v>
+      </c>
+      <c r="C7" t="s">
+        <v>44</v>
+      </c>
+      <c r="D7" t="s">
+        <v>62</v>
+      </c>
+      <c r="E7" t="s">
+        <v>9</v>
+      </c>
+      <c r="F7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G7">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8">
+        <v>19330051920161</v>
+      </c>
+      <c r="B8" t="s">
+        <v>20</v>
+      </c>
+      <c r="C8" t="s">
+        <v>45</v>
+      </c>
+      <c r="D8" t="s">
+        <v>63</v>
+      </c>
+      <c r="E8" t="s">
+        <v>9</v>
+      </c>
+      <c r="F8" t="s">
+        <v>12</v>
+      </c>
+      <c r="G8">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9">
+        <v>21330051920251</v>
+      </c>
+      <c r="B9" t="s">
+        <v>25</v>
+      </c>
+      <c r="C9" t="s">
+        <v>46</v>
+      </c>
+      <c r="D9" t="s">
+        <v>64</v>
+      </c>
+      <c r="E9" t="s">
+        <v>8</v>
+      </c>
+      <c r="F9" t="s">
+        <v>10</v>
+      </c>
+      <c r="G9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10">
+        <v>21330051920255</v>
+      </c>
+      <c r="B10" t="s">
+        <v>26</v>
+      </c>
+      <c r="C10" t="s">
+        <v>20</v>
+      </c>
+      <c r="D10" t="s">
+        <v>65</v>
+      </c>
+      <c r="E10" t="s">
+        <v>8</v>
+      </c>
+      <c r="F10" t="s">
+        <v>10</v>
+      </c>
+      <c r="G10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11">
+        <v>21330051920265</v>
+      </c>
+      <c r="B11" t="s">
+        <v>27</v>
+      </c>
+      <c r="C11" t="s">
+        <v>47</v>
+      </c>
+      <c r="D11" t="s">
+        <v>66</v>
+      </c>
+      <c r="E11" t="s">
+        <v>8</v>
+      </c>
+      <c r="F11" t="s">
+        <v>10</v>
+      </c>
+      <c r="G11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12">
+        <v>21330051920267</v>
+      </c>
+      <c r="B12" t="s">
+        <v>28</v>
+      </c>
+      <c r="C12" t="s">
+        <v>48</v>
+      </c>
+      <c r="D12" t="s">
+        <v>67</v>
+      </c>
+      <c r="E12" t="s">
+        <v>8</v>
+      </c>
+      <c r="F12" t="s">
+        <v>10</v>
+      </c>
+      <c r="G12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="A13">
+        <v>21330051920358</v>
+      </c>
+      <c r="B13" t="s">
+        <v>29</v>
+      </c>
+      <c r="C13" t="s">
+        <v>49</v>
+      </c>
+      <c r="D13" t="s">
+        <v>68</v>
+      </c>
+      <c r="E13" t="s">
+        <v>8</v>
+      </c>
+      <c r="F13" t="s">
+        <v>10</v>
+      </c>
+      <c r="G13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="A14">
+        <v>21330051920268</v>
+      </c>
+      <c r="B14" t="s">
+        <v>30</v>
+      </c>
+      <c r="C14" t="s">
+        <v>50</v>
+      </c>
+      <c r="D14" t="s">
+        <v>69</v>
+      </c>
+      <c r="E14" t="s">
+        <v>8</v>
+      </c>
+      <c r="F14" t="s">
+        <v>10</v>
+      </c>
+      <c r="G14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
+      <c r="A15">
+        <v>21330051920361</v>
+      </c>
+      <c r="B15" t="s">
+        <v>31</v>
+      </c>
+      <c r="C15" t="s">
+        <v>44</v>
+      </c>
+      <c r="D15" t="s">
+        <v>70</v>
+      </c>
+      <c r="E15" t="s">
+        <v>8</v>
+      </c>
+      <c r="F15" t="s">
+        <v>10</v>
+      </c>
+      <c r="G15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
+      <c r="A16">
+        <v>21330051920290</v>
+      </c>
+      <c r="B16" t="s">
+        <v>32</v>
+      </c>
+      <c r="C16" t="s">
+        <v>20</v>
+      </c>
+      <c r="D16" t="s">
+        <v>71</v>
+      </c>
+      <c r="E16" t="s">
+        <v>8</v>
+      </c>
+      <c r="F16" t="s">
+        <v>11</v>
+      </c>
+      <c r="G16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7">
+      <c r="A17">
+        <v>21330051920293</v>
+      </c>
+      <c r="B17" t="s">
+        <v>33</v>
+      </c>
+      <c r="C17" t="s">
+        <v>35</v>
+      </c>
+      <c r="D17" t="s">
+        <v>72</v>
+      </c>
+      <c r="E17" t="s">
+        <v>8</v>
+      </c>
+      <c r="F17" t="s">
+        <v>11</v>
+      </c>
+      <c r="G17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7">
+      <c r="A18">
+        <v>21330051920296</v>
+      </c>
+      <c r="B18" t="s">
+        <v>34</v>
+      </c>
+      <c r="C18" t="s">
+        <v>51</v>
+      </c>
+      <c r="D18" t="s">
+        <v>73</v>
+      </c>
+      <c r="E18" t="s">
+        <v>8</v>
+      </c>
+      <c r="F18" t="s">
+        <v>11</v>
+      </c>
+      <c r="G18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7">
+      <c r="A19">
+        <v>21330051920303</v>
+      </c>
+      <c r="B19" t="s">
+        <v>35</v>
+      </c>
+      <c r="C19" t="s">
+        <v>52</v>
+      </c>
+      <c r="D19" t="s">
+        <v>74</v>
+      </c>
+      <c r="E19" t="s">
+        <v>8</v>
+      </c>
+      <c r="F19" t="s">
+        <v>11</v>
+      </c>
+      <c r="G19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7">
+      <c r="A20">
+        <v>21330051920305</v>
+      </c>
+      <c r="B20" t="s">
+        <v>36</v>
+      </c>
+      <c r="C20" t="s">
+        <v>53</v>
+      </c>
+      <c r="D20" t="s">
+        <v>75</v>
+      </c>
+      <c r="E20" t="s">
+        <v>8</v>
+      </c>
+      <c r="F20" t="s">
+        <v>11</v>
+      </c>
+      <c r="G20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7">
+      <c r="A21">
+        <v>21330051920308</v>
+      </c>
+      <c r="B21" t="s">
+        <v>37</v>
+      </c>
+      <c r="C21" t="s">
+        <v>54</v>
+      </c>
+      <c r="D21" t="s">
+        <v>76</v>
+      </c>
+      <c r="E21" t="s">
+        <v>8</v>
+      </c>
+      <c r="F21" t="s">
+        <v>11</v>
+      </c>
+      <c r="G21">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7">
+      <c r="A22">
+        <v>21330051920311</v>
+      </c>
+      <c r="B22" t="s">
+        <v>38</v>
+      </c>
+      <c r="C22" t="s">
+        <v>55</v>
+      </c>
+      <c r="D22" t="s">
+        <v>77</v>
+      </c>
+      <c r="E22" t="s">
+        <v>8</v>
+      </c>
+      <c r="F22" t="s">
+        <v>11</v>
+      </c>
+      <c r="G22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7">
+      <c r="A23">
+        <v>21330051920312</v>
+      </c>
+      <c r="B23" t="s">
+        <v>39</v>
+      </c>
+      <c r="C23" t="s">
+        <v>44</v>
+      </c>
+      <c r="D23" t="s">
+        <v>78</v>
+      </c>
+      <c r="E23" t="s">
+        <v>8</v>
+      </c>
+      <c r="F23" t="s">
+        <v>11</v>
+      </c>
+      <c r="G23">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7">
+      <c r="A24">
+        <v>21330051920319</v>
+      </c>
+      <c r="B24" t="s">
+        <v>40</v>
+      </c>
+      <c r="C24" t="s">
+        <v>20</v>
+      </c>
+      <c r="D24" t="s">
+        <v>79</v>
+      </c>
+      <c r="E24" t="s">
+        <v>8</v>
+      </c>
+      <c r="F24" t="s">
+        <v>11</v>
+      </c>
+      <c r="G24">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7">
+      <c r="A25">
+        <v>21330051920321</v>
+      </c>
+      <c r="B25" t="s">
+        <v>31</v>
+      </c>
+      <c r="C25" t="s">
+        <v>56</v>
+      </c>
+      <c r="D25" t="s">
+        <v>80</v>
+      </c>
+      <c r="E25" t="s">
+        <v>8</v>
+      </c>
+      <c r="F25" t="s">
+        <v>11</v>
+      </c>
+      <c r="G25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7">
+      <c r="A26">
+        <v>21330051920323</v>
+      </c>
+      <c r="B26" t="s">
+        <v>41</v>
+      </c>
+      <c r="C26" t="s">
+        <v>44</v>
+      </c>
+      <c r="D26" t="s">
+        <v>81</v>
+      </c>
+      <c r="E26" t="s">
+        <v>8</v>
+      </c>
+      <c r="F26" t="s">
+        <v>11</v>
+      </c>
+      <c r="G26">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/docentes/Caballero Rosas María Teresa - Estadisticos 20212.xlsx
+++ b/docentes/Caballero Rosas María Teresa - Estadisticos 20212.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="174" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="36">
   <si>
     <t>Mat</t>
   </si>
@@ -79,138 +79,45 @@
     <t>ALDUCIN</t>
   </si>
   <si>
+    <t>FRANCO</t>
+  </si>
+  <si>
+    <t>COUDER</t>
+  </si>
+  <si>
+    <t>ACEVEDO</t>
+  </si>
+  <si>
+    <t>DOMINGUEZ</t>
+  </si>
+  <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
     <t>HERNANDEZ</t>
   </si>
   <si>
-    <t>MIXCOHUA</t>
-  </si>
-  <si>
-    <t>FRANCO</t>
-  </si>
-  <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
-    <t>COUDER</t>
-  </si>
-  <si>
-    <t>ACEVEDO</t>
-  </si>
-  <si>
-    <t>DOMINGUEZ</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
-    <t>MADRAZO</t>
-  </si>
-  <si>
-    <t>MORALES</t>
-  </si>
-  <si>
-    <t>NAVARRO</t>
-  </si>
-  <si>
-    <t>REYES</t>
-  </si>
-  <si>
-    <t>ARIAS</t>
-  </si>
-  <si>
     <t>CASTILLO</t>
   </si>
   <si>
-    <t>CHICO</t>
-  </si>
-  <si>
-    <t>HUERTA</t>
-  </si>
-  <si>
-    <t>JUSTO</t>
-  </si>
-  <si>
-    <t>MOTA</t>
-  </si>
-  <si>
-    <t>OFICIAL</t>
-  </si>
-  <si>
-    <t>OLMOS</t>
-  </si>
-  <si>
-    <t>RAMOS</t>
-  </si>
-  <si>
-    <t>ROMERO</t>
-  </si>
-  <si>
-    <t>CAMPOS</t>
-  </si>
-  <si>
-    <t>IXMATLAHUA</t>
-  </si>
-  <si>
     <t>SANCHEZ</t>
   </si>
   <si>
-    <t>TETLA</t>
-  </si>
-  <si>
     <t>VALENCIA</t>
   </si>
   <si>
     <t>GARCIA</t>
   </si>
   <si>
-    <t>0</t>
-  </si>
-  <si>
-    <t>DE LA CRUZ</t>
-  </si>
-  <si>
-    <t>BENITO</t>
-  </si>
-  <si>
-    <t>GIL</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>NEGRETE</t>
-  </si>
-  <si>
-    <t>CERON</t>
-  </si>
-  <si>
-    <t>VILLASEÑOR</t>
-  </si>
-  <si>
-    <t>SOLANO</t>
-  </si>
-  <si>
     <t>MELANI PAOLA</t>
   </si>
   <si>
-    <t>MARIA TERESA</t>
-  </si>
-  <si>
-    <t>ANGELINA</t>
-  </si>
-  <si>
     <t>CRISTOPHER</t>
   </si>
   <si>
-    <t>JOSE RAFAEL</t>
-  </si>
-  <si>
     <t>YULIANA</t>
   </si>
   <si>
-    <t>JESE YAEL</t>
-  </si>
-  <si>
     <t>YARELI</t>
   </si>
   <si>
@@ -218,51 +125,6 @@
   </si>
   <si>
     <t>RICARDO ABEL</t>
-  </si>
-  <si>
-    <t>ANGELO RENE</t>
-  </si>
-  <si>
-    <t>DULCE MARIA</t>
-  </si>
-  <si>
-    <t>DULCE NAOMI</t>
-  </si>
-  <si>
-    <t>DUILIO</t>
-  </si>
-  <si>
-    <t>JAZMIN</t>
-  </si>
-  <si>
-    <t>VANESSA</t>
-  </si>
-  <si>
-    <t>ATZIRI</t>
-  </si>
-  <si>
-    <t>YULIET</t>
-  </si>
-  <si>
-    <t>MARIA MICHELLE</t>
-  </si>
-  <si>
-    <t>ANGEL DIEGO</t>
-  </si>
-  <si>
-    <t>MONICA AIME</t>
-  </si>
-  <si>
-    <t>ARACELY</t>
-  </si>
-  <si>
-    <t>SAYURI BETSABE</t>
-  </si>
-  <si>
-    <t>ANA LAURA</t>
-  </si>
-  <si>
-    <t>DIEGO EMILIO</t>
   </si>
 </sst>
 </file>
@@ -663,10 +525,10 @@
         <v>44</v>
       </c>
       <c r="D2">
+        <v>0</v>
+      </c>
+      <c r="E2">
         <v>12</v>
-      </c>
-      <c r="E2">
-        <v>0</v>
       </c>
       <c r="F2">
         <v>32</v>
@@ -675,7 +537,7 @@
         <v>72.73</v>
       </c>
       <c r="H2">
-        <v>7.7</v>
+        <v>7</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -689,10 +551,10 @@
         <v>44</v>
       </c>
       <c r="D3">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="F3">
         <v>28</v>
@@ -701,7 +563,7 @@
         <v>63.64</v>
       </c>
       <c r="H3">
-        <v>6.6</v>
+        <v>6.1</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -712,10 +574,10 @@
         <v>12</v>
       </c>
       <c r="C4">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E4">
         <v>3</v>
@@ -724,7 +586,7 @@
         <v>31</v>
       </c>
       <c r="G4">
-        <v>88.56999999999999</v>
+        <v>91.18000000000001</v>
       </c>
       <c r="H4">
         <v>8.6</v>
@@ -780,16 +642,19 @@
         <v>44</v>
       </c>
       <c r="D2">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>32</v>
+        <v>5</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>88.64</v>
+      </c>
+      <c r="H2">
+        <v>7</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -803,16 +668,19 @@
         <v>44</v>
       </c>
       <c r="D3">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>30</v>
+        <v>2</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>95.45</v>
+      </c>
+      <c r="H3">
+        <v>6.1</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -823,19 +691,22 @@
         <v>12</v>
       </c>
       <c r="C4">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D4">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>34</v>
+        <v>1</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>97.06</v>
+      </c>
+      <c r="H4">
+        <v>8.6</v>
       </c>
     </row>
   </sheetData>
@@ -888,19 +759,19 @@
         <v>44</v>
       </c>
       <c r="D2">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F2">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="G2">
-        <v>72.73</v>
+        <v>88.64</v>
       </c>
       <c r="H2">
-        <v>7.7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -914,19 +785,19 @@
         <v>44</v>
       </c>
       <c r="D3">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="E3">
         <v>2</v>
       </c>
       <c r="F3">
-        <v>28</v>
+        <v>42</v>
       </c>
       <c r="G3">
-        <v>63.64</v>
+        <v>95.45</v>
       </c>
       <c r="H3">
-        <v>6.7</v>
+        <v>7.8</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -937,22 +808,22 @@
         <v>12</v>
       </c>
       <c r="C4">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D4">
+        <v>0</v>
+      </c>
+      <c r="E4">
         <v>1</v>
       </c>
-      <c r="E4">
-        <v>3</v>
-      </c>
       <c r="F4">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="G4">
-        <v>88.56999999999999</v>
+        <v>97.06</v>
       </c>
       <c r="H4">
-        <v>8.6</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -962,7 +833,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G26"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1000,10 +871,10 @@
         <v>19</v>
       </c>
       <c r="C2" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="D2" t="s">
-        <v>57</v>
+        <v>30</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1017,22 +888,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>21330051920260</v>
+        <v>21330051920337</v>
       </c>
       <c r="B3" t="s">
         <v>20</v>
       </c>
       <c r="C3" t="s">
-        <v>42</v>
+        <v>26</v>
       </c>
       <c r="D3" t="s">
-        <v>58</v>
+        <v>31</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
       </c>
       <c r="F3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G3">
         <v>2</v>
@@ -1040,22 +911,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>21330051920088</v>
+        <v>19330051920276</v>
       </c>
       <c r="B4" t="s">
         <v>21</v>
       </c>
       <c r="C4" t="s">
-        <v>43</v>
+        <v>27</v>
       </c>
       <c r="D4" t="s">
-        <v>59</v>
+        <v>32</v>
       </c>
       <c r="E4" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F4" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G4">
         <v>2</v>
@@ -1063,507 +934,70 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>21330051920337</v>
+        <v>21330051920251</v>
       </c>
       <c r="B5" t="s">
         <v>22</v>
       </c>
       <c r="C5" t="s">
+        <v>28</v>
+      </c>
+      <c r="D5" t="s">
         <v>33</v>
       </c>
-      <c r="D5" t="s">
-        <v>60</v>
-      </c>
       <c r="E5" t="s">
         <v>8</v>
       </c>
       <c r="F5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G5">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>20330051920235</v>
+        <v>21330051920255</v>
       </c>
       <c r="B6" t="s">
         <v>23</v>
       </c>
       <c r="C6" t="s">
-        <v>44</v>
+        <v>25</v>
       </c>
       <c r="D6" t="s">
-        <v>61</v>
+        <v>34</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
       </c>
       <c r="F6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>19330051920276</v>
+        <v>21330051920265</v>
       </c>
       <c r="B7" t="s">
         <v>24</v>
       </c>
       <c r="C7" t="s">
-        <v>44</v>
+        <v>29</v>
       </c>
       <c r="D7" t="s">
-        <v>62</v>
+        <v>35</v>
       </c>
       <c r="E7" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F7" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G7">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8">
-        <v>19330051920161</v>
-      </c>
-      <c r="B8" t="s">
-        <v>20</v>
-      </c>
-      <c r="C8" t="s">
-        <v>45</v>
-      </c>
-      <c r="D8" t="s">
-        <v>63</v>
-      </c>
-      <c r="E8" t="s">
-        <v>9</v>
-      </c>
-      <c r="F8" t="s">
-        <v>12</v>
-      </c>
-      <c r="G8">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9">
-        <v>21330051920251</v>
-      </c>
-      <c r="B9" t="s">
-        <v>25</v>
-      </c>
-      <c r="C9" t="s">
-        <v>46</v>
-      </c>
-      <c r="D9" t="s">
-        <v>64</v>
-      </c>
-      <c r="E9" t="s">
-        <v>8</v>
-      </c>
-      <c r="F9" t="s">
-        <v>10</v>
-      </c>
-      <c r="G9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10">
-        <v>21330051920255</v>
-      </c>
-      <c r="B10" t="s">
-        <v>26</v>
-      </c>
-      <c r="C10" t="s">
-        <v>20</v>
-      </c>
-      <c r="D10" t="s">
-        <v>65</v>
-      </c>
-      <c r="E10" t="s">
-        <v>8</v>
-      </c>
-      <c r="F10" t="s">
-        <v>10</v>
-      </c>
-      <c r="G10">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11">
-        <v>21330051920265</v>
-      </c>
-      <c r="B11" t="s">
-        <v>27</v>
-      </c>
-      <c r="C11" t="s">
-        <v>47</v>
-      </c>
-      <c r="D11" t="s">
-        <v>66</v>
-      </c>
-      <c r="E11" t="s">
-        <v>8</v>
-      </c>
-      <c r="F11" t="s">
-        <v>10</v>
-      </c>
-      <c r="G11">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="A12">
-        <v>21330051920267</v>
-      </c>
-      <c r="B12" t="s">
-        <v>28</v>
-      </c>
-      <c r="C12" t="s">
-        <v>48</v>
-      </c>
-      <c r="D12" t="s">
-        <v>67</v>
-      </c>
-      <c r="E12" t="s">
-        <v>8</v>
-      </c>
-      <c r="F12" t="s">
-        <v>10</v>
-      </c>
-      <c r="G12">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
-      <c r="A13">
-        <v>21330051920358</v>
-      </c>
-      <c r="B13" t="s">
-        <v>29</v>
-      </c>
-      <c r="C13" t="s">
-        <v>49</v>
-      </c>
-      <c r="D13" t="s">
-        <v>68</v>
-      </c>
-      <c r="E13" t="s">
-        <v>8</v>
-      </c>
-      <c r="F13" t="s">
-        <v>10</v>
-      </c>
-      <c r="G13">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
-      <c r="A14">
-        <v>21330051920268</v>
-      </c>
-      <c r="B14" t="s">
-        <v>30</v>
-      </c>
-      <c r="C14" t="s">
-        <v>50</v>
-      </c>
-      <c r="D14" t="s">
-        <v>69</v>
-      </c>
-      <c r="E14" t="s">
-        <v>8</v>
-      </c>
-      <c r="F14" t="s">
-        <v>10</v>
-      </c>
-      <c r="G14">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7">
-      <c r="A15">
-        <v>21330051920361</v>
-      </c>
-      <c r="B15" t="s">
-        <v>31</v>
-      </c>
-      <c r="C15" t="s">
-        <v>44</v>
-      </c>
-      <c r="D15" t="s">
-        <v>70</v>
-      </c>
-      <c r="E15" t="s">
-        <v>8</v>
-      </c>
-      <c r="F15" t="s">
-        <v>10</v>
-      </c>
-      <c r="G15">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7">
-      <c r="A16">
-        <v>21330051920290</v>
-      </c>
-      <c r="B16" t="s">
-        <v>32</v>
-      </c>
-      <c r="C16" t="s">
-        <v>20</v>
-      </c>
-      <c r="D16" t="s">
-        <v>71</v>
-      </c>
-      <c r="E16" t="s">
-        <v>8</v>
-      </c>
-      <c r="F16" t="s">
-        <v>11</v>
-      </c>
-      <c r="G16">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7">
-      <c r="A17">
-        <v>21330051920293</v>
-      </c>
-      <c r="B17" t="s">
-        <v>33</v>
-      </c>
-      <c r="C17" t="s">
-        <v>35</v>
-      </c>
-      <c r="D17" t="s">
-        <v>72</v>
-      </c>
-      <c r="E17" t="s">
-        <v>8</v>
-      </c>
-      <c r="F17" t="s">
-        <v>11</v>
-      </c>
-      <c r="G17">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7">
-      <c r="A18">
-        <v>21330051920296</v>
-      </c>
-      <c r="B18" t="s">
-        <v>34</v>
-      </c>
-      <c r="C18" t="s">
-        <v>51</v>
-      </c>
-      <c r="D18" t="s">
-        <v>73</v>
-      </c>
-      <c r="E18" t="s">
-        <v>8</v>
-      </c>
-      <c r="F18" t="s">
-        <v>11</v>
-      </c>
-      <c r="G18">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7">
-      <c r="A19">
-        <v>21330051920303</v>
-      </c>
-      <c r="B19" t="s">
-        <v>35</v>
-      </c>
-      <c r="C19" t="s">
-        <v>52</v>
-      </c>
-      <c r="D19" t="s">
-        <v>74</v>
-      </c>
-      <c r="E19" t="s">
-        <v>8</v>
-      </c>
-      <c r="F19" t="s">
-        <v>11</v>
-      </c>
-      <c r="G19">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7">
-      <c r="A20">
-        <v>21330051920305</v>
-      </c>
-      <c r="B20" t="s">
-        <v>36</v>
-      </c>
-      <c r="C20" t="s">
-        <v>53</v>
-      </c>
-      <c r="D20" t="s">
-        <v>75</v>
-      </c>
-      <c r="E20" t="s">
-        <v>8</v>
-      </c>
-      <c r="F20" t="s">
-        <v>11</v>
-      </c>
-      <c r="G20">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7">
-      <c r="A21">
-        <v>21330051920308</v>
-      </c>
-      <c r="B21" t="s">
-        <v>37</v>
-      </c>
-      <c r="C21" t="s">
-        <v>54</v>
-      </c>
-      <c r="D21" t="s">
-        <v>76</v>
-      </c>
-      <c r="E21" t="s">
-        <v>8</v>
-      </c>
-      <c r="F21" t="s">
-        <v>11</v>
-      </c>
-      <c r="G21">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7">
-      <c r="A22">
-        <v>21330051920311</v>
-      </c>
-      <c r="B22" t="s">
-        <v>38</v>
-      </c>
-      <c r="C22" t="s">
-        <v>55</v>
-      </c>
-      <c r="D22" t="s">
-        <v>77</v>
-      </c>
-      <c r="E22" t="s">
-        <v>8</v>
-      </c>
-      <c r="F22" t="s">
-        <v>11</v>
-      </c>
-      <c r="G22">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7">
-      <c r="A23">
-        <v>21330051920312</v>
-      </c>
-      <c r="B23" t="s">
-        <v>39</v>
-      </c>
-      <c r="C23" t="s">
-        <v>44</v>
-      </c>
-      <c r="D23" t="s">
-        <v>78</v>
-      </c>
-      <c r="E23" t="s">
-        <v>8</v>
-      </c>
-      <c r="F23" t="s">
-        <v>11</v>
-      </c>
-      <c r="G23">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7">
-      <c r="A24">
-        <v>21330051920319</v>
-      </c>
-      <c r="B24" t="s">
-        <v>40</v>
-      </c>
-      <c r="C24" t="s">
-        <v>20</v>
-      </c>
-      <c r="D24" t="s">
-        <v>79</v>
-      </c>
-      <c r="E24" t="s">
-        <v>8</v>
-      </c>
-      <c r="F24" t="s">
-        <v>11</v>
-      </c>
-      <c r="G24">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7">
-      <c r="A25">
-        <v>21330051920321</v>
-      </c>
-      <c r="B25" t="s">
-        <v>31</v>
-      </c>
-      <c r="C25" t="s">
-        <v>56</v>
-      </c>
-      <c r="D25" t="s">
-        <v>80</v>
-      </c>
-      <c r="E25" t="s">
-        <v>8</v>
-      </c>
-      <c r="F25" t="s">
-        <v>11</v>
-      </c>
-      <c r="G25">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7">
-      <c r="A26">
-        <v>21330051920323</v>
-      </c>
-      <c r="B26" t="s">
-        <v>41</v>
-      </c>
-      <c r="C26" t="s">
-        <v>44</v>
-      </c>
-      <c r="D26" t="s">
-        <v>81</v>
-      </c>
-      <c r="E26" t="s">
-        <v>8</v>
-      </c>
-      <c r="F26" t="s">
-        <v>11</v>
-      </c>
-      <c r="G26">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Caballero Rosas María Teresa - Estadisticos 20212.xlsx
+++ b/docentes/Caballero Rosas María Teresa - Estadisticos 20212.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="33">
   <si>
     <t>Mat</t>
   </si>
@@ -76,22 +76,25 @@
     <t>Reprobadas</t>
   </si>
   <si>
-    <t>ALDUCIN</t>
+    <t>COUDER</t>
+  </si>
+  <si>
+    <t>ACEVEDO</t>
+  </si>
+  <si>
+    <t>DOMINGUEZ</t>
+  </si>
+  <si>
+    <t>DOLORES</t>
   </si>
   <si>
     <t>FRANCO</t>
   </si>
   <si>
-    <t>COUDER</t>
-  </si>
-  <si>
-    <t>ACEVEDO</t>
-  </si>
-  <si>
-    <t>DOMINGUEZ</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
+    <t>VALENCIA</t>
   </si>
   <si>
     <t>HERNANDEZ</t>
@@ -100,31 +103,19 @@
     <t>CASTILLO</t>
   </si>
   <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>VALENCIA</t>
-  </si>
-  <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>MELANI PAOLA</t>
+    <t>YULIANA</t>
+  </si>
+  <si>
+    <t>YARELI</t>
+  </si>
+  <si>
+    <t>JESUS EMMANUEL</t>
+  </si>
+  <si>
+    <t>AMISADAI</t>
   </si>
   <si>
     <t>CRISTOPHER</t>
-  </si>
-  <si>
-    <t>YULIANA</t>
-  </si>
-  <si>
-    <t>YARELI</t>
-  </si>
-  <si>
-    <t>JESUS EMMANUEL</t>
-  </si>
-  <si>
-    <t>RICARDO ABEL</t>
   </si>
 </sst>
 </file>
@@ -833,7 +824,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -865,22 +856,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>21330051920252</v>
+        <v>19330051920276</v>
       </c>
       <c r="B2" t="s">
         <v>19</v>
       </c>
       <c r="C2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D2" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="E2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F2" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G2">
         <v>2</v>
@@ -888,68 +879,68 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>21330051920337</v>
+        <v>21330051920251</v>
       </c>
       <c r="B3" t="s">
         <v>20</v>
       </c>
       <c r="C3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D3" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
       </c>
       <c r="F3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>19330051920276</v>
+        <v>21330051920255</v>
       </c>
       <c r="B4" t="s">
         <v>21</v>
       </c>
       <c r="C4" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D4" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="E4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F4" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G4">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>21330051920251</v>
+        <v>21330051920298</v>
       </c>
       <c r="B5" t="s">
         <v>22</v>
       </c>
       <c r="C5" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D5" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
       </c>
       <c r="F5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G5">
         <v>1</v>
@@ -957,47 +948,24 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>21330051920255</v>
+        <v>21330051920337</v>
       </c>
       <c r="B6" t="s">
         <v>23</v>
       </c>
       <c r="C6" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D6" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
       </c>
       <c r="F6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7">
-        <v>21330051920265</v>
-      </c>
-      <c r="B7" t="s">
-        <v>24</v>
-      </c>
-      <c r="C7" t="s">
-        <v>29</v>
-      </c>
-      <c r="D7" t="s">
-        <v>35</v>
-      </c>
-      <c r="E7" t="s">
-        <v>8</v>
-      </c>
-      <c r="F7" t="s">
-        <v>10</v>
-      </c>
-      <c r="G7">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Caballero Rosas María Teresa - Estadisticos 20212.xlsx
+++ b/docentes/Caballero Rosas María Teresa - Estadisticos 20212.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="22">
   <si>
     <t>Mat</t>
   </si>
@@ -76,46 +76,13 @@
     <t>Reprobadas</t>
   </si>
   <si>
-    <t>COUDER</t>
-  </si>
-  <si>
-    <t>ACEVEDO</t>
-  </si>
-  <si>
-    <t>DOMINGUEZ</t>
-  </si>
-  <si>
-    <t>DOLORES</t>
-  </si>
-  <si>
-    <t>FRANCO</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>VALENCIA</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>CASTILLO</t>
-  </si>
-  <si>
-    <t>YULIANA</t>
-  </si>
-  <si>
-    <t>YARELI</t>
-  </si>
-  <si>
-    <t>JESUS EMMANUEL</t>
-  </si>
-  <si>
-    <t>AMISADAI</t>
-  </si>
-  <si>
-    <t>CRISTOPHER</t>
+    <t>MOTA</t>
+  </si>
+  <si>
+    <t>CERON</t>
+  </si>
+  <si>
+    <t>ANGEL DIEGO</t>
   </si>
 </sst>
 </file>
@@ -753,16 +720,16 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F2">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="G2">
-        <v>88.64</v>
+        <v>93.18000000000001</v>
       </c>
       <c r="H2">
-        <v>8</v>
+        <v>8.1</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -779,16 +746,16 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F3">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G3">
-        <v>95.45</v>
+        <v>97.73</v>
       </c>
       <c r="H3">
-        <v>7.8</v>
+        <v>7.9</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -805,13 +772,13 @@
         <v>0</v>
       </c>
       <c r="E4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F4">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G4">
-        <v>97.06</v>
+        <v>100</v>
       </c>
       <c r="H4">
         <v>9</v>
@@ -824,7 +791,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:G2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -856,117 +823,25 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>19330051920276</v>
+        <v>21330051920308</v>
       </c>
       <c r="B2" t="s">
         <v>19</v>
       </c>
       <c r="C2" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="D2" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="E2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G2">
         <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
-      <c r="A3">
-        <v>21330051920251</v>
-      </c>
-      <c r="B3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C3" t="s">
-        <v>25</v>
-      </c>
-      <c r="D3" t="s">
-        <v>29</v>
-      </c>
-      <c r="E3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F3" t="s">
-        <v>10</v>
-      </c>
-      <c r="G3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4">
-        <v>21330051920255</v>
-      </c>
-      <c r="B4" t="s">
-        <v>21</v>
-      </c>
-      <c r="C4" t="s">
-        <v>26</v>
-      </c>
-      <c r="D4" t="s">
-        <v>30</v>
-      </c>
-      <c r="E4" t="s">
-        <v>8</v>
-      </c>
-      <c r="F4" t="s">
-        <v>10</v>
-      </c>
-      <c r="G4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5">
-        <v>21330051920298</v>
-      </c>
-      <c r="B5" t="s">
-        <v>22</v>
-      </c>
-      <c r="C5" t="s">
-        <v>26</v>
-      </c>
-      <c r="D5" t="s">
-        <v>31</v>
-      </c>
-      <c r="E5" t="s">
-        <v>8</v>
-      </c>
-      <c r="F5" t="s">
-        <v>11</v>
-      </c>
-      <c r="G5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6">
-        <v>21330051920337</v>
-      </c>
-      <c r="B6" t="s">
-        <v>23</v>
-      </c>
-      <c r="C6" t="s">
-        <v>27</v>
-      </c>
-      <c r="D6" t="s">
-        <v>32</v>
-      </c>
-      <c r="E6" t="s">
-        <v>8</v>
-      </c>
-      <c r="F6" t="s">
-        <v>11</v>
-      </c>
-      <c r="G6">
-        <v>1</v>
       </c>
     </row>
   </sheetData>
